--- a/pages/shp/uploads/18-06-2026 - 18-06-2026.xlsx
+++ b/pages/shp/uploads/18-06-2026 - 18-06-2026.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1537" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1547" uniqueCount="441">
   <si>
     <t>NOMOR AJU</t>
   </si>
@@ -444,6 +444,18 @@
   </si>
   <si>
     <t>LK</t>
+  </si>
+  <si>
+    <t>054230</t>
+  </si>
+  <si>
+    <t>2026-06-19</t>
+  </si>
+  <si>
+    <t>0002</t>
+  </si>
+  <si>
+    <t>01940000</t>
   </si>
   <si>
     <t>IDCGK</t>
@@ -1390,7 +1402,7 @@
     <t>30966</t>
   </si>
   <si>
-    <t>2026-06-19</t>
+    <t>2026-07-15</t>
   </si>
   <si>
     <t>368913/PM/KPU.1/2026</t>
@@ -2526,14 +2538,26 @@
       <c r="AH6" t="s">
         <v>136</v>
       </c>
+      <c r="AJ6" t="s">
+        <v>137</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>138</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>139</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>140</v>
+      </c>
       <c r="AO6" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AR6" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="AS6" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AV6" t="s">
         <v>116</v>
@@ -2626,7 +2650,7 @@
         <v>134</v>
       </c>
       <c r="CP6" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="CQ6" t="s">
         <v>117</v>
@@ -2643,7 +2667,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B7" t="s">
         <v>105</v>
@@ -2679,7 +2703,7 @@
         <v>114</v>
       </c>
       <c r="AR7" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="AS7" t="s">
         <v>114</v>
@@ -2775,7 +2799,7 @@
         <v>106</v>
       </c>
       <c r="CP7" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="CQ7" t="s">
         <v>117</v>
@@ -2792,7 +2816,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B8" t="s">
         <v>105</v>
@@ -2852,22 +2876,22 @@
         <v>119</v>
       </c>
       <c r="BK8" t="n">
-        <v>79.09</v>
+        <v>78.47</v>
       </c>
       <c r="BL8" t="n">
         <v>0.0</v>
       </c>
       <c r="BN8" t="n">
-        <v>33265.87</v>
+        <v>33003.73</v>
       </c>
       <c r="BO8" t="n">
-        <v>79.09</v>
+        <v>78.47</v>
       </c>
       <c r="BP8" t="n">
-        <v>1886.17</v>
+        <v>1871.31</v>
       </c>
       <c r="BQ8" t="n">
-        <v>33265.87</v>
+        <v>33003.73</v>
       </c>
       <c r="BR8" t="n">
         <v>0.0</v>
@@ -2924,7 +2948,7 @@
         <v>106</v>
       </c>
       <c r="CP8" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="CQ8" t="s">
         <v>117</v>
@@ -2941,7 +2965,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B9" t="s">
         <v>105</v>
@@ -3007,7 +3031,7 @@
         <v>0.0</v>
       </c>
       <c r="BN9" t="n">
-        <v>6504.42</v>
+        <v>6272.37</v>
       </c>
       <c r="BO9" t="n">
         <v>15.46</v>
@@ -3016,7 +3040,7 @@
         <v>368.8</v>
       </c>
       <c r="BQ9" t="n">
-        <v>6504.42</v>
+        <v>6272.37</v>
       </c>
       <c r="BR9" t="n">
         <v>0.0</v>
@@ -3073,7 +3097,7 @@
         <v>106</v>
       </c>
       <c r="CP9" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="CQ9" t="s">
         <v>117</v>
@@ -3117,13 +3141,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -3154,10 +3178,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>
@@ -3187,13 +3211,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -3227,10 +3251,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>61</v>
@@ -3242,7 +3266,7 @@
         <v>67</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -3300,64 +3324,64 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>77</v>
@@ -3372,52 +3396,52 @@
         <v>69</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>71</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>74</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
   </sheetData>
@@ -3469,76 +3493,76 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -3572,19 +3596,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -3617,16 +3641,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -3667,28 +3691,28 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>
@@ -3718,13 +3742,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="2">
@@ -3738,7 +3762,7 @@
         <v>135</v>
       </c>
       <c r="D2" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="3">
@@ -3752,7 +3776,7 @@
         <v>135</v>
       </c>
       <c r="D3" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="4">
@@ -3766,7 +3790,7 @@
         <v>135</v>
       </c>
       <c r="D4" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="5">
@@ -3780,7 +3804,7 @@
         <v>135</v>
       </c>
       <c r="D5" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="6">
@@ -3794,12 +3818,12 @@
         <v>135</v>
       </c>
       <c r="D6" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
@@ -3808,12 +3832,12 @@
         <v>135</v>
       </c>
       <c r="D7" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B8" t="n">
         <v>1</v>
@@ -3822,12 +3846,12 @@
         <v>135</v>
       </c>
       <c r="D8" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B9" t="n">
         <v>1</v>
@@ -3836,7 +3860,7 @@
         <v>135</v>
       </c>
       <c r="D9" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
   </sheetData>
@@ -3879,49 +3903,49 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2">
@@ -3938,19 +3962,19 @@
         <v>112</v>
       </c>
       <c r="E2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="G2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="H2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="J2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3">
@@ -3958,28 +3982,28 @@
         <v>104</v>
       </c>
       <c r="B3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D3" t="s">
         <v>112</v>
       </c>
       <c r="E3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="F3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="G3" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="I3" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="J3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="O3" t="s">
         <v>108</v>
@@ -3990,22 +4014,22 @@
         <v>104</v>
       </c>
       <c r="B4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C4" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D4" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="F4" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="G4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5">
@@ -4013,16 +4037,16 @@
         <v>104</v>
       </c>
       <c r="B5" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C5" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="G5" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="M5" t="s">
         <v>113</v>
@@ -4039,10 +4063,10 @@
         <v>112</v>
       </c>
       <c r="F6" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="G6" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="M6" t="s">
         <v>113</v>
@@ -4053,16 +4077,16 @@
         <v>127</v>
       </c>
       <c r="B7" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C7" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F7" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="G7" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="M7" t="s">
         <v>113</v>
@@ -4079,13 +4103,13 @@
         <v>112</v>
       </c>
       <c r="F8" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="G8" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="M8" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="9">
@@ -4093,28 +4117,28 @@
         <v>127</v>
       </c>
       <c r="B9" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C9" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D9" t="s">
         <v>112</v>
       </c>
       <c r="E9" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="F9" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="G9" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="I9" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="J9" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="O9" t="s">
         <v>108</v>
@@ -4125,22 +4149,22 @@
         <v>127</v>
       </c>
       <c r="B10" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C10" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D10" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E10" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="F10" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="G10" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11">
@@ -4157,19 +4181,19 @@
         <v>112</v>
       </c>
       <c r="E11" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F11" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="G11" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="H11" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="J11" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12">
@@ -4186,19 +4210,19 @@
         <v>112</v>
       </c>
       <c r="E12" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F12" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="G12" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="H12" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="J12" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -4206,28 +4230,28 @@
         <v>129</v>
       </c>
       <c r="B13" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C13" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D13" t="s">
         <v>112</v>
       </c>
       <c r="E13" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="F13" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="G13" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="I13" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="J13" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="O13" t="s">
         <v>108</v>
@@ -4238,22 +4262,22 @@
         <v>129</v>
       </c>
       <c r="B14" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C14" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D14" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E14" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="F14" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="G14" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="15">
@@ -4267,10 +4291,10 @@
         <v>112</v>
       </c>
       <c r="F15" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="G15" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="M15" t="s">
         <v>113</v>
@@ -4281,16 +4305,16 @@
         <v>129</v>
       </c>
       <c r="B16" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C16" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F16" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="G16" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="M16" t="s">
         <v>113</v>
@@ -4307,10 +4331,10 @@
         <v>112</v>
       </c>
       <c r="F17" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="G17" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="M17" t="s">
         <v>113</v>
@@ -4330,19 +4354,19 @@
         <v>112</v>
       </c>
       <c r="E18" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F18" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="G18" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="H18" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="J18" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19">
@@ -4350,16 +4374,16 @@
         <v>131</v>
       </c>
       <c r="B19" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C19" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F19" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="G19" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="M19" t="s">
         <v>113</v>
@@ -4370,28 +4394,28 @@
         <v>131</v>
       </c>
       <c r="B20" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C20" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D20" t="s">
         <v>112</v>
       </c>
       <c r="E20" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="F20" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="G20" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="I20" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="J20" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="O20" t="s">
         <v>108</v>
@@ -4402,22 +4426,22 @@
         <v>131</v>
       </c>
       <c r="B21" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C21" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D21" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E21" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="F21" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="G21" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="22">
@@ -4434,19 +4458,19 @@
         <v>112</v>
       </c>
       <c r="E22" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F22" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="G22" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="H22" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="J22" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23">
@@ -4454,28 +4478,28 @@
         <v>133</v>
       </c>
       <c r="B23" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C23" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D23" t="s">
         <v>112</v>
       </c>
       <c r="E23" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="F23" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G23" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="I23" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="J23" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="O23" t="s">
         <v>108</v>
@@ -4492,10 +4516,10 @@
         <v>112</v>
       </c>
       <c r="F24" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="G24" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="M24" t="s">
         <v>136</v>
@@ -4506,22 +4530,22 @@
         <v>133</v>
       </c>
       <c r="B25" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C25" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D25" t="s">
         <v>112</v>
       </c>
       <c r="E25" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F25" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="G25" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26">
@@ -4529,16 +4553,16 @@
         <v>133</v>
       </c>
       <c r="B26" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C26" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F26" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="G26" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="M26" t="s">
         <v>136</v>
@@ -4546,7 +4570,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B27" t="s">
         <v>118</v>
@@ -4558,48 +4582,48 @@
         <v>112</v>
       </c>
       <c r="E27" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F27" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="G27" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="H27" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="J27" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B28" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C28" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D28" t="s">
         <v>112</v>
       </c>
       <c r="E28" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="F28" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="G28" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="I28" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="J28" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="O28" t="s">
         <v>108</v>
@@ -4607,30 +4631,30 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B29" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C29" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D29" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E29" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="F29" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="G29" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B30" t="s">
         <v>112</v>
@@ -4639,10 +4663,10 @@
         <v>112</v>
       </c>
       <c r="F30" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="G30" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="M30" t="s">
         <v>113</v>
@@ -4650,19 +4674,19 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B31" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C31" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F31" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="G31" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="M31" t="s">
         <v>113</v>
@@ -4670,31 +4694,31 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B32" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C32" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D32" t="s">
         <v>112</v>
       </c>
       <c r="E32" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="F32" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="G32" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="I32" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="J32" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="O32" t="s">
         <v>108</v>
@@ -4702,30 +4726,30 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B33" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C33" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D33" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E33" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="F33" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="G33" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B34" t="s">
         <v>118</v>
@@ -4737,36 +4761,36 @@
         <v>112</v>
       </c>
       <c r="E34" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F34" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="G34" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="H34" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="J34" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B35" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C35" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F35" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="G35" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="M35" t="s">
         <v>113</v>
@@ -4774,7 +4798,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B36" t="s">
         <v>112</v>
@@ -4783,42 +4807,42 @@
         <v>112</v>
       </c>
       <c r="F36" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="G36" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="M36" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B37" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C37" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D37" t="s">
         <v>112</v>
       </c>
       <c r="E37" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="F37" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="G37" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="I37" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="J37" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="O37" t="s">
         <v>108</v>
@@ -4826,30 +4850,30 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B38" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C38" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D38" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E38" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="F38" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="G38" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B39" t="s">
         <v>118</v>
@@ -4861,36 +4885,36 @@
         <v>112</v>
       </c>
       <c r="E39" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F39" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="G39" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="H39" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="J39" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B40" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C40" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F40" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="G40" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="M40" t="s">
         <v>113</v>
@@ -4898,7 +4922,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B41" t="s">
         <v>112</v>
@@ -4907,13 +4931,13 @@
         <v>112</v>
       </c>
       <c r="F41" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="G41" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="M41" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -4936,12 +4960,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
   </sheetData>
@@ -4973,24 +4997,24 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C1" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="D1" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B2" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="C2" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="D2" t="s">
         <v>117</v>
@@ -4998,38 +5022,35 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B3" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="D3" t="s">
-        <v>429</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="B4" t="s">
-        <v>426</v>
-      </c>
-      <c r="C4" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D4" t="s">
-        <v>117</v>
+        <v>433</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B5" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="C5" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="D5" t="s">
         <v>117</v>
@@ -5037,13 +5058,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B6" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="C6" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="D6" t="s">
         <v>117</v>
@@ -5051,13 +5072,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B7" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="C7" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="D7" t="s">
         <v>117</v>
@@ -5065,13 +5086,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="B8" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="C8" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D8" t="s">
         <v>117</v>
@@ -5079,13 +5100,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>140</v>
+        <v>104</v>
       </c>
       <c r="B9" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="C9" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="D9" t="s">
         <v>117</v>
@@ -5093,16 +5114,41 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B10" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="C10" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="D10" t="s">
         <v>117</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>149</v>
+      </c>
+      <c r="B11" t="s">
+        <v>430</v>
+      </c>
+      <c r="C11" t="s">
+        <v>440</v>
+      </c>
+      <c r="D11" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>149</v>
+      </c>
+      <c r="B12" t="s">
+        <v>432</v>
+      </c>
+      <c r="D12" t="s">
+        <v>433</v>
       </c>
     </row>
   </sheetData>
@@ -5136,22 +5182,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2">
@@ -5162,13 +5208,13 @@
         <v>1.0</v>
       </c>
       <c r="C2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3">
@@ -5179,10 +5225,10 @@
         <v>2.0</v>
       </c>
       <c r="C3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D3" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E3" t="s">
         <v>117</v>
@@ -5196,10 +5242,10 @@
         <v>3.0</v>
       </c>
       <c r="C4" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="D4" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E4" t="s">
         <v>117</v>
@@ -5213,13 +5259,13 @@
         <v>4.0</v>
       </c>
       <c r="C5" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D5" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="E5" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6">
@@ -5230,13 +5276,13 @@
         <v>5.0</v>
       </c>
       <c r="C6" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D6" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E6" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7">
@@ -5247,13 +5293,13 @@
         <v>6.0</v>
       </c>
       <c r="C7" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D7" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E7" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8">
@@ -5264,13 +5310,13 @@
         <v>7.0</v>
       </c>
       <c r="C8" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D8" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="E8" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9">
@@ -5281,13 +5327,13 @@
         <v>8.0</v>
       </c>
       <c r="C9" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D9" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E9" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10">
@@ -5298,13 +5344,13 @@
         <v>1.0</v>
       </c>
       <c r="C10" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D10" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E10" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11">
@@ -5315,10 +5361,10 @@
         <v>2.0</v>
       </c>
       <c r="C11" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D11" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="E11" t="s">
         <v>117</v>
@@ -5332,10 +5378,10 @@
         <v>3.0</v>
       </c>
       <c r="C12" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="D12" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="E12" t="s">
         <v>117</v>
@@ -5349,13 +5395,13 @@
         <v>1.0</v>
       </c>
       <c r="C13" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D13" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E13" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="14">
@@ -5366,10 +5412,10 @@
         <v>2.0</v>
       </c>
       <c r="C14" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D14" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E14" t="s">
         <v>117</v>
@@ -5383,10 +5429,10 @@
         <v>3.0</v>
       </c>
       <c r="C15" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="D15" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E15" t="s">
         <v>117</v>
@@ -5400,13 +5446,13 @@
         <v>4.0</v>
       </c>
       <c r="C16" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D16" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="E16" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="17">
@@ -5417,13 +5463,13 @@
         <v>5.0</v>
       </c>
       <c r="C17" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D17" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E17" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="18">
@@ -5434,13 +5480,13 @@
         <v>6.0</v>
       </c>
       <c r="C18" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D18" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E18" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
     </row>
     <row r="19">
@@ -5451,13 +5497,13 @@
         <v>7.0</v>
       </c>
       <c r="C19" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D19" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E19" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="20">
@@ -5468,13 +5514,13 @@
         <v>8.0</v>
       </c>
       <c r="C20" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D20" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E20" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="21">
@@ -5485,13 +5531,13 @@
         <v>9.0</v>
       </c>
       <c r="C21" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D21" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E21" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="22">
@@ -5502,13 +5548,13 @@
         <v>10.0</v>
       </c>
       <c r="C22" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D22" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E22" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="23">
@@ -5519,13 +5565,13 @@
         <v>1.0</v>
       </c>
       <c r="C23" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D23" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E23" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="24">
@@ -5536,10 +5582,10 @@
         <v>2.0</v>
       </c>
       <c r="C24" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D24" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="E24" t="s">
         <v>117</v>
@@ -5553,10 +5599,10 @@
         <v>3.0</v>
       </c>
       <c r="C25" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="D25" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="E25" t="s">
         <v>117</v>
@@ -5570,13 +5616,13 @@
         <v>4.0</v>
       </c>
       <c r="C26" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D26" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E26" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
     <row r="27">
@@ -5587,13 +5633,13 @@
         <v>1.0</v>
       </c>
       <c r="C27" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D27" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E27" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="28">
@@ -5604,10 +5650,10 @@
         <v>2.0</v>
       </c>
       <c r="C28" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D28" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E28" t="s">
         <v>117</v>
@@ -5621,10 +5667,10 @@
         <v>3.0</v>
       </c>
       <c r="C29" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="D29" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="E29" t="s">
         <v>117</v>
@@ -5638,10 +5684,10 @@
         <v>4.0</v>
       </c>
       <c r="C30" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D30" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="E30" t="s">
         <v>117</v>
@@ -5655,10 +5701,10 @@
         <v>5.0</v>
       </c>
       <c r="C31" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D31" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="E31" t="s">
         <v>117</v>
@@ -5672,10 +5718,10 @@
         <v>6.0</v>
       </c>
       <c r="C32" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D32" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="E32" t="s">
         <v>117</v>
@@ -5689,10 +5735,10 @@
         <v>7.0</v>
       </c>
       <c r="C33" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D33" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E33" t="s">
         <v>117</v>
@@ -5700,33 +5746,33 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B34" t="n">
         <v>1.0</v>
       </c>
       <c r="C34" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D34" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E34" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B35" t="n">
         <v>2.0</v>
       </c>
       <c r="C35" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D35" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E35" t="s">
         <v>117</v>
@@ -5734,16 +5780,16 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B36" t="n">
         <v>3.0</v>
       </c>
       <c r="C36" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="D36" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E36" t="s">
         <v>117</v>
@@ -5751,152 +5797,152 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B37" t="n">
         <v>4.0</v>
       </c>
       <c r="C37" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D37" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="E37" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B38" t="n">
         <v>5.0</v>
       </c>
       <c r="C38" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D38" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E38" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B39" t="n">
         <v>6.0</v>
       </c>
       <c r="C39" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D39" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E39" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B40" t="n">
         <v>7.0</v>
       </c>
       <c r="C40" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D40" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E40" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B41" t="n">
         <v>8.0</v>
       </c>
       <c r="C41" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D41" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E41" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B42" t="n">
         <v>9.0</v>
       </c>
       <c r="C42" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D42" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E42" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B43" t="n">
         <v>10.0</v>
       </c>
       <c r="C43" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D43" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E43" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B44" t="n">
         <v>1.0</v>
       </c>
       <c r="C44" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D44" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E44" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B45" t="n">
         <v>2.0</v>
       </c>
       <c r="C45" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D45" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="E45" t="s">
         <v>117</v>
@@ -5904,16 +5950,16 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B46" t="n">
         <v>3.0</v>
       </c>
       <c r="C46" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="D46" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="E46" t="s">
         <v>117</v>
@@ -5921,33 +5967,33 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B47" t="n">
         <v>1.0</v>
       </c>
       <c r="C47" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D47" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E47" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B48" t="n">
         <v>2.0</v>
       </c>
       <c r="C48" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D48" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="E48" t="s">
         <v>117</v>
@@ -5955,16 +6001,16 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B49" t="n">
         <v>3.0</v>
       </c>
       <c r="C49" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="D49" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="E49" t="s">
         <v>117</v>
@@ -6003,28 +6049,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2">
@@ -6038,13 +6084,13 @@
         <v>108</v>
       </c>
       <c r="D2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="E2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3">
@@ -6058,13 +6104,13 @@
         <v>108</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="E3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="F3" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4">
@@ -6078,13 +6124,13 @@
         <v>108</v>
       </c>
       <c r="D4" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="E4" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F4" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5">
@@ -6098,13 +6144,13 @@
         <v>108</v>
       </c>
       <c r="D5" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="E5" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F5" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6">
@@ -6115,21 +6161,21 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="E6" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="F6" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
@@ -6138,18 +6184,18 @@
         <v>108</v>
       </c>
       <c r="D7" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="E7" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F7" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B8" t="n">
         <v>1</v>
@@ -6158,18 +6204,18 @@
         <v>108</v>
       </c>
       <c r="D8" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="E8" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="F8" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B9" t="n">
         <v>1</v>
@@ -6178,13 +6224,13 @@
         <v>108</v>
       </c>
       <c r="D9" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="E9" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="F9" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -6217,19 +6263,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="2">
@@ -6240,13 +6286,13 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D2" t="n">
         <v>35</v>
       </c>
       <c r="E2" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3">
@@ -6257,13 +6303,13 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D3" t="n">
         <v>63</v>
       </c>
       <c r="E3" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4">
@@ -6274,13 +6320,13 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D4" t="n">
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5">
@@ -6291,13 +6337,13 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D5" t="n">
         <v>54</v>
       </c>
       <c r="E5" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="6">
@@ -6308,64 +6354,64 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D7" t="n">
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D8" t="n">
         <v>592</v>
       </c>
       <c r="E8" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D9" t="n">
         <v>92</v>
       </c>
       <c r="E9" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -6399,22 +6445,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>278</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>274</v>
       </c>
     </row>
   </sheetData>
@@ -6456,61 +6502,61 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>60</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
   </sheetData>
@@ -6598,58 +6644,58 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>77</v>
@@ -6661,19 +6707,19 @@
         <v>78</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>69</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="AB1" s="1" t="s">
         <v>71</v>
@@ -6688,25 +6734,25 @@
         <v>64</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="AM1" s="1" t="s">
         <v>61</v>
@@ -6715,94 +6761,94 @@
         <v>74</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="AS1" s="1" t="s">
         <v>30</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="AU1" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="BO1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="2">
@@ -6813,34 +6859,34 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D2" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="E2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="F2" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="G2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="H2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="I2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="J2" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="K2" t="n">
         <v>2255.0</v>
       </c>
       <c r="L2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="M2" t="n">
         <v>24.0</v>
@@ -6885,10 +6931,10 @@
         <v>0.0</v>
       </c>
       <c r="AS2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AY2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="BJ2" t="n">
         <v>0.0</v>
@@ -6908,34 +6954,34 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D3" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="E3" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="F3" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="G3" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="H3" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="I3" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="J3" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="K3" t="n">
         <v>902.0</v>
       </c>
       <c r="L3" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="M3" t="n">
         <v>11.0</v>
@@ -6980,10 +7026,10 @@
         <v>0.0</v>
       </c>
       <c r="AS3" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AY3" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="BJ3" t="n">
         <v>0.0</v>
@@ -7003,34 +7049,34 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
+        <v>346</v>
+      </c>
+      <c r="D4" t="s">
+        <v>347</v>
+      </c>
+      <c r="E4" t="s">
+        <v>348</v>
+      </c>
+      <c r="F4" t="s">
+        <v>249</v>
+      </c>
+      <c r="G4" t="s">
+        <v>249</v>
+      </c>
+      <c r="H4" t="s">
+        <v>249</v>
+      </c>
+      <c r="I4" t="s">
+        <v>249</v>
+      </c>
+      <c r="J4" t="s">
         <v>342</v>
-      </c>
-      <c r="D4" t="s">
-        <v>343</v>
-      </c>
-      <c r="E4" t="s">
-        <v>344</v>
-      </c>
-      <c r="F4" t="s">
-        <v>245</v>
-      </c>
-      <c r="G4" t="s">
-        <v>245</v>
-      </c>
-      <c r="H4" t="s">
-        <v>245</v>
-      </c>
-      <c r="I4" t="s">
-        <v>245</v>
-      </c>
-      <c r="J4" t="s">
-        <v>338</v>
       </c>
       <c r="K4" t="n">
         <v>1766.0</v>
       </c>
       <c r="L4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="M4" t="n">
         <v>63.0</v>
@@ -7075,10 +7121,10 @@
         <v>0.0</v>
       </c>
       <c r="AS4" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AY4" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="BJ4" t="n">
         <v>0.0</v>
@@ -7098,34 +7144,34 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D5" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="E5" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="F5" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="G5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="H5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="I5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="J5" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="K5" t="n">
         <v>1830.0</v>
       </c>
       <c r="L5" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="M5" t="n">
         <v>11.0</v>
@@ -7170,10 +7216,10 @@
         <v>0.0</v>
       </c>
       <c r="AS5" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AY5" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="BJ5" t="n">
         <v>0.0</v>
@@ -7193,34 +7239,34 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D6" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="E6" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="F6" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="G6" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="H6" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="I6" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="J6" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="K6" t="n">
         <v>170.0</v>
       </c>
       <c r="L6" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="M6" t="n">
         <v>1.0</v>
@@ -7265,10 +7311,10 @@
         <v>0.0</v>
       </c>
       <c r="AS6" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AY6" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="BJ6" t="n">
         <v>0.0</v>
@@ -7288,34 +7334,34 @@
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D7" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="E7" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="F7" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="G7" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="H7" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="I7" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="J7" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="K7" t="n">
         <v>1991.0</v>
       </c>
       <c r="L7" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="M7" t="n">
         <v>24.0</v>
@@ -7360,10 +7406,10 @@
         <v>0.0</v>
       </c>
       <c r="AS7" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AY7" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="BJ7" t="n">
         <v>0.0</v>
@@ -7383,34 +7429,34 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D8" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="E8" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="F8" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="G8" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="H8" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="I8" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="J8" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="K8" t="n">
         <v>2815.0</v>
       </c>
       <c r="L8" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="M8" t="n">
         <v>30.0</v>
@@ -7455,10 +7501,10 @@
         <v>0.0</v>
       </c>
       <c r="AS8" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AY8" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="BJ8" t="n">
         <v>0.0</v>
@@ -7478,34 +7524,34 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="D9" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="E9" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F9" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="G9" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="H9" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="I9" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="J9" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="K9" t="n">
         <v>24.0</v>
       </c>
       <c r="L9" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="M9" t="n">
         <v>1.0</v>
@@ -7550,10 +7596,10 @@
         <v>0.0</v>
       </c>
       <c r="AS9" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AY9" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="BJ9" t="n">
         <v>0.0</v>
@@ -7567,40 +7613,40 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D10" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="E10" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="F10" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="G10" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="H10" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="I10" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="J10" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="K10" t="n">
         <v>510.0</v>
       </c>
       <c r="L10" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="M10" t="n">
         <v>3.0</v>
@@ -7645,10 +7691,10 @@
         <v>0.0</v>
       </c>
       <c r="AS10" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AY10" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="BJ10" t="n">
         <v>0.0</v>
@@ -7662,40 +7708,40 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B11" t="n">
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D11" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="E11" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F11" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="G11" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="H11" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="I11" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="J11" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="K11" t="n">
         <v>1490.0</v>
       </c>
       <c r="L11" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="M11" t="n">
         <v>9.0</v>
@@ -7740,10 +7786,10 @@
         <v>0.0</v>
       </c>
       <c r="AS11" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AY11" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="BJ11" t="n">
         <v>0.0</v>
@@ -7757,40 +7803,40 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B12" t="n">
         <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D12" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="E12" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="F12" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="G12" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="H12" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="I12" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="J12" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="K12" t="n">
         <v>2257.0</v>
       </c>
       <c r="L12" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="M12" t="n">
         <v>81.0</v>
@@ -7835,10 +7881,10 @@
         <v>0.0</v>
       </c>
       <c r="AS12" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AY12" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="BJ12" t="n">
         <v>0.0</v>
@@ -7852,40 +7898,40 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B13" t="n">
         <v>3</v>
       </c>
       <c r="C13" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D13" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="E13" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="F13" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="G13" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="H13" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="I13" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="J13" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="K13" t="n">
         <v>2492.0</v>
       </c>
       <c r="L13" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="M13" t="n">
         <v>89.0</v>
@@ -7930,10 +7976,10 @@
         <v>0.0</v>
       </c>
       <c r="AS13" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AY13" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="BJ13" t="n">
         <v>0.0</v>
@@ -7947,40 +7993,40 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B14" t="n">
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D14" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="E14" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="F14" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="G14" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="H14" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="I14" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="J14" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="K14" t="n">
         <v>1345.0</v>
       </c>
       <c r="L14" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="M14" t="n">
         <v>50.0</v>
@@ -8025,10 +8071,10 @@
         <v>0.0</v>
       </c>
       <c r="AS14" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AY14" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="BJ14" t="n">
         <v>0.0</v>
@@ -8042,40 +8088,40 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B15" t="n">
         <v>6</v>
       </c>
       <c r="C15" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D15" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="E15" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="F15" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="G15" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="H15" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="I15" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="J15" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="K15" t="n">
         <v>518.0</v>
       </c>
       <c r="L15" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="M15" t="n">
         <v>24.0</v>
@@ -8120,10 +8166,10 @@
         <v>0.0</v>
       </c>
       <c r="AS15" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AY15" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="BJ15" t="n">
         <v>0.0</v>
@@ -8137,40 +8183,40 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B16" t="n">
         <v>7</v>
       </c>
       <c r="C16" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D16" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="E16" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="F16" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="G16" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="H16" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="I16" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="J16" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="K16" t="n">
         <v>1024.0</v>
       </c>
       <c r="L16" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="M16" t="n">
         <v>37.0</v>
@@ -8215,10 +8261,10 @@
         <v>0.0</v>
       </c>
       <c r="AS16" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AY16" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="BJ16" t="n">
         <v>0.0</v>
@@ -8232,40 +8278,40 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B17" t="n">
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D17" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="E17" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F17" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="G17" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="H17" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="I17" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="J17" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="K17" t="n">
         <v>1542.0</v>
       </c>
       <c r="L17" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="M17" t="n">
         <v>43.0</v>
@@ -8283,7 +8329,7 @@
         <v>18037.0</v>
       </c>
       <c r="AC17" t="n">
-        <v>4317.6</v>
+        <v>4055.46</v>
       </c>
       <c r="AF17" t="n">
         <v>0.0</v>
@@ -8298,7 +8344,7 @@
         <v>0.0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="AK17" t="n">
         <v>0.0</v>
@@ -8310,10 +8356,10 @@
         <v>0.0</v>
       </c>
       <c r="AS17" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AY17" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="BJ17" t="n">
         <v>0.0</v>
@@ -8327,40 +8373,40 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="s">
+        <v>346</v>
+      </c>
+      <c r="D18" t="s">
+        <v>372</v>
+      </c>
+      <c r="E18" t="s">
+        <v>373</v>
+      </c>
+      <c r="F18" t="s">
+        <v>249</v>
+      </c>
+      <c r="G18" t="s">
+        <v>249</v>
+      </c>
+      <c r="H18" t="s">
+        <v>249</v>
+      </c>
+      <c r="I18" t="s">
+        <v>249</v>
+      </c>
+      <c r="J18" t="s">
         <v>342</v>
-      </c>
-      <c r="D18" t="s">
-        <v>368</v>
-      </c>
-      <c r="E18" t="s">
-        <v>369</v>
-      </c>
-      <c r="F18" t="s">
-        <v>245</v>
-      </c>
-      <c r="G18" t="s">
-        <v>245</v>
-      </c>
-      <c r="H18" t="s">
-        <v>245</v>
-      </c>
-      <c r="I18" t="s">
-        <v>245</v>
-      </c>
-      <c r="J18" t="s">
-        <v>338</v>
       </c>
       <c r="K18" t="n">
         <v>2645.0</v>
       </c>
       <c r="L18" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="M18" t="n">
         <v>115.0</v>
@@ -8405,10 +8451,10 @@
         <v>0.0</v>
       </c>
       <c r="AS18" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AY18" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="BJ18" t="n">
         <v>0.0</v>
@@ -8422,40 +8468,40 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B19" t="n">
         <v>4</v>
       </c>
       <c r="C19" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D19" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="E19" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="F19" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="G19" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="H19" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="I19" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="J19" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="K19" t="n">
         <v>517.0</v>
       </c>
       <c r="L19" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="M19" t="n">
         <v>24.0</v>
@@ -8500,10 +8546,10 @@
         <v>0.0</v>
       </c>
       <c r="AS19" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AY19" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="BJ19" t="n">
         <v>0.0</v>
@@ -8517,40 +8563,40 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B20" t="n">
         <v>8</v>
       </c>
       <c r="C20" t="s">
+        <v>346</v>
+      </c>
+      <c r="D20" t="s">
+        <v>372</v>
+      </c>
+      <c r="E20" t="s">
+        <v>375</v>
+      </c>
+      <c r="F20" t="s">
+        <v>249</v>
+      </c>
+      <c r="G20" t="s">
+        <v>249</v>
+      </c>
+      <c r="H20" t="s">
+        <v>249</v>
+      </c>
+      <c r="I20" t="s">
+        <v>249</v>
+      </c>
+      <c r="J20" t="s">
         <v>342</v>
-      </c>
-      <c r="D20" t="s">
-        <v>368</v>
-      </c>
-      <c r="E20" t="s">
-        <v>371</v>
-      </c>
-      <c r="F20" t="s">
-        <v>245</v>
-      </c>
-      <c r="G20" t="s">
-        <v>245</v>
-      </c>
-      <c r="H20" t="s">
-        <v>245</v>
-      </c>
-      <c r="I20" t="s">
-        <v>245</v>
-      </c>
-      <c r="J20" t="s">
-        <v>338</v>
       </c>
       <c r="K20" t="n">
         <v>2969.0</v>
       </c>
       <c r="L20" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="M20" t="n">
         <v>129.0</v>
@@ -8595,10 +8641,10 @@
         <v>0.0</v>
       </c>
       <c r="AS20" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AY20" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="BJ20" t="n">
         <v>0.0</v>
@@ -8612,40 +8658,40 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="s">
+        <v>346</v>
+      </c>
+      <c r="D21" t="s">
+        <v>347</v>
+      </c>
+      <c r="E21" t="s">
+        <v>376</v>
+      </c>
+      <c r="F21" t="s">
+        <v>249</v>
+      </c>
+      <c r="G21" t="s">
+        <v>249</v>
+      </c>
+      <c r="H21" t="s">
+        <v>249</v>
+      </c>
+      <c r="I21" t="s">
+        <v>249</v>
+      </c>
+      <c r="J21" t="s">
         <v>342</v>
-      </c>
-      <c r="D21" t="s">
-        <v>343</v>
-      </c>
-      <c r="E21" t="s">
-        <v>372</v>
-      </c>
-      <c r="F21" t="s">
-        <v>245</v>
-      </c>
-      <c r="G21" t="s">
-        <v>245</v>
-      </c>
-      <c r="H21" t="s">
-        <v>245</v>
-      </c>
-      <c r="I21" t="s">
-        <v>245</v>
-      </c>
-      <c r="J21" t="s">
-        <v>338</v>
       </c>
       <c r="K21" t="n">
         <v>1482.0</v>
       </c>
       <c r="L21" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="M21" t="n">
         <v>54.0</v>
@@ -8690,10 +8736,10 @@
         <v>0.0</v>
       </c>
       <c r="AS21" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AY21" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="BJ21" t="n">
         <v>0.0</v>
@@ -8707,40 +8753,40 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B22" t="n">
         <v>2</v>
       </c>
       <c r="C22" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D22" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="E22" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F22" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="G22" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="H22" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="I22" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="J22" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="K22" t="n">
         <v>1365.0</v>
       </c>
       <c r="L22" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="M22" t="n">
         <v>38.0</v>
@@ -8758,7 +8804,7 @@
         <v>18037.0</v>
       </c>
       <c r="AC22" t="n">
-        <v>3822.0</v>
+        <v>3589.95</v>
       </c>
       <c r="AF22" t="n">
         <v>0.0</v>
@@ -8773,7 +8819,7 @@
         <v>0.0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="AK22" t="n">
         <v>0.0</v>
@@ -8785,10 +8831,10 @@
         <v>0.0</v>
       </c>
       <c r="AS22" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AY22" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="BJ22" t="n">
         <v>0.0</v>
@@ -8843,58 +8889,58 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>
